--- a/COLM.xlsx
+++ b/COLM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16C1ACD-9897-4316-B117-DF48B73C8E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989DD108-AD8D-495F-8C82-82CC5F410679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{ECC62F7A-C70F-47CF-9717-8932D5683754}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{ECC62F7A-C70F-47CF-9717-8932D5683754}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -264,13 +264,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -365,33 +371,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -765,7 +774,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>58.06</v>
+        <v>56.92</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -773,10 +782,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>51.140793000000002</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>54</v>
+        <v>51.193193999999998</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -788,7 +797,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>2969.2344415800003</v>
+        <v>2913.9166024800002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -799,11 +808,11 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <f>319.341+216.013</f>
-        <v>535.35400000000004</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>54</v>
+        <f>532.305+92.296</f>
+        <v>624.601</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -813,8 +822,8 @@
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="17" t="s">
-        <v>54</v>
+      <c r="J6" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -826,7 +835,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>2433.8804415800005</v>
+        <v>2289.3156024800001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -955,7 +964,9 @@
       <c r="O3" s="12">
         <v>690.149</v>
       </c>
-      <c r="P3" s="12"/>
+      <c r="P3" s="12">
+        <v>556.226</v>
+      </c>
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
@@ -1020,7 +1031,9 @@
       <c r="O4" s="12">
         <v>37.162999999999997</v>
       </c>
-      <c r="P4" s="12"/>
+      <c r="P4" s="12">
+        <v>16.282</v>
+      </c>
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
@@ -1085,7 +1098,9 @@
       <c r="O5" s="12">
         <v>26.661000000000001</v>
       </c>
-      <c r="P5" s="12"/>
+      <c r="P5" s="12">
+        <v>23.324999999999999</v>
+      </c>
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
@@ -1150,7 +1165,9 @@
       <c r="O6" s="12">
         <v>25.04</v>
       </c>
-      <c r="P6" s="12"/>
+      <c r="P6" s="12">
+        <v>18.529</v>
+      </c>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
@@ -1229,6 +1246,9 @@
       <c r="O7" s="12">
         <v>623.09299999999996</v>
       </c>
+      <c r="P7" s="12">
+        <v>497.36799999999999</v>
+      </c>
       <c r="U7" s="12">
         <v>2712.7539999999999</v>
       </c>
@@ -1271,6 +1291,9 @@
       <c r="O8" s="12">
         <v>155.91999999999999</v>
       </c>
+      <c r="P8" s="12">
+        <v>116.994</v>
+      </c>
       <c r="U8" s="12">
         <v>682.98800000000006</v>
       </c>
@@ -1313,6 +1336,9 @@
       <c r="O9" s="12">
         <v>401.072</v>
       </c>
+      <c r="P9" s="12">
+        <v>318.35300000000001</v>
+      </c>
       <c r="U9" s="12">
         <v>1777.0930000000001</v>
       </c>
@@ -1355,6 +1381,9 @@
       <c r="O10" s="12">
         <v>377.94099999999997</v>
       </c>
+      <c r="P10" s="12">
+        <v>296.09989999999999</v>
+      </c>
       <c r="U10" s="12">
         <v>1618.6489999999999</v>
       </c>
@@ -1399,6 +1428,9 @@
       <c r="O11" s="13">
         <v>779.01300000000003</v>
       </c>
+      <c r="P11" s="13">
+        <v>614.36199999999997</v>
+      </c>
       <c r="T11" s="13">
         <v>3487.203</v>
       </c>
@@ -1444,6 +1476,9 @@
       <c r="O12" s="12">
         <v>384.05099999999999</v>
       </c>
+      <c r="P12" s="12">
+        <v>255.93</v>
+      </c>
       <c r="T12" s="12">
         <v>1757.271</v>
       </c>
@@ -1511,6 +1546,10 @@
         <f t="shared" si="1"/>
         <v>394.96200000000005</v>
       </c>
+      <c r="P13" s="12">
+        <f t="shared" si="1"/>
+        <v>358.43199999999996</v>
+      </c>
       <c r="T13" s="12">
         <f t="shared" si="1"/>
         <v>1729.932</v>
@@ -1561,6 +1600,9 @@
       <c r="O14" s="12">
         <v>357.137</v>
       </c>
+      <c r="P14" s="12">
+        <v>332.19099999999997</v>
+      </c>
       <c r="T14" s="12">
         <f>1416.313+25</f>
         <v>1441.3130000000001</v>
@@ -1608,6 +1650,9 @@
       <c r="O15" s="12">
         <v>4.1680000000000001</v>
       </c>
+      <c r="P15" s="12">
+        <v>4.6429999999999998</v>
+      </c>
       <c r="T15" s="12">
         <v>21.664999999999999</v>
       </c>
@@ -1675,6 +1720,10 @@
         <f t="shared" si="3"/>
         <v>41.993000000000045</v>
       </c>
+      <c r="P16" s="12">
+        <f t="shared" si="3"/>
+        <v>30.883999999999986</v>
+      </c>
       <c r="T16" s="12">
         <f t="shared" si="3"/>
         <v>310.28399999999993</v>
@@ -1723,6 +1772,9 @@
       <c r="O17" s="12">
         <v>4.883</v>
       </c>
+      <c r="P17" s="12">
+        <v>6.2160000000000002</v>
+      </c>
       <c r="T17" s="12">
         <v>13.686999999999999</v>
       </c>
@@ -1768,6 +1820,9 @@
       <c r="O18" s="12">
         <v>0.39700000000000002</v>
       </c>
+      <c r="P18" s="12">
+        <v>-0.81499999999999995</v>
+      </c>
       <c r="T18" s="12">
         <v>2.2210000000000001</v>
       </c>
@@ -1835,6 +1890,10 @@
         <f t="shared" si="5"/>
         <v>47.273000000000046</v>
       </c>
+      <c r="P19" s="12">
+        <f t="shared" si="5"/>
+        <v>36.284999999999982</v>
+      </c>
       <c r="T19" s="12">
         <f t="shared" si="5"/>
         <v>326.19199999999995</v>
@@ -1883,6 +1942,9 @@
       <c r="O20" s="12">
         <v>12.965</v>
       </c>
+      <c r="P20" s="12">
+        <v>9.7319999999999993</v>
+      </c>
       <c r="T20" s="12">
         <v>74.792000000000002</v>
       </c>
@@ -1950,6 +2012,10 @@
         <f t="shared" si="7"/>
         <v>34.30800000000005</v>
       </c>
+      <c r="P21" s="12">
+        <f t="shared" si="7"/>
+        <v>26.552999999999983</v>
+      </c>
       <c r="T21" s="12">
         <f t="shared" si="7"/>
         <v>251.39999999999995</v>
@@ -2023,7 +2089,10 @@
         <f t="shared" si="9"/>
         <v>0.65190871605829803</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <f t="shared" si="9"/>
+        <v>0.51891733437561038</v>
+      </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="3"/>
@@ -2109,7 +2178,9 @@
       <c r="O24" s="3">
         <v>52.627000000000002</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>51.17</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -2246,14 +2317,17 @@
         <v>1.2510624962436934E-2</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" ref="N26:O26" si="15">+N11/J11-1</f>
+        <f t="shared" ref="N26:P26" si="15">+N11/J11-1</f>
         <v>-1</v>
       </c>
       <c r="O26" s="10">
         <f t="shared" si="15"/>
         <v>7.2066100414680534E-4</v>
       </c>
-      <c r="P26" s="10"/>
+      <c r="P26" s="10">
+        <f t="shared" si="15"/>
+        <v>1.5061644356179071E-2</v>
+      </c>
       <c r="Q26" s="10"/>
       <c r="R26" s="10"/>
       <c r="S26" s="3"/>
@@ -2352,10 +2426,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" ref="O27" si="19">+O13/O11</f>
+        <f t="shared" ref="O27:P27" si="19">+O13/O11</f>
         <v>0.50700309237458174</v>
       </c>
-      <c r="P27" s="8"/>
+      <c r="P27" s="8">
+        <f t="shared" si="19"/>
+        <v>0.58342150067875287</v>
+      </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="3"/>
@@ -2457,10 +2534,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="8">
-        <f t="shared" ref="O28" si="23">+O16/O11</f>
+        <f t="shared" ref="O28:P28" si="23">+O16/O11</f>
         <v>5.3905390539053959E-2</v>
       </c>
-      <c r="P28" s="8"/>
+      <c r="P28" s="8">
+        <f t="shared" si="23"/>
+        <v>5.0270036232709689E-2</v>
+      </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="3"/>
@@ -2562,10 +2642,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" ref="O29" si="27">+O20/O19</f>
+        <f t="shared" ref="O29:P29" si="27">+O20/O19</f>
         <v>0.27425803312673169</v>
       </c>
-      <c r="P29" s="8"/>
+      <c r="P29" s="8">
+        <f t="shared" si="27"/>
+        <v>0.26821000413393975</v>
+      </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="3"/>
